--- a/backend/sample_files/IT_A_Internal_Marks_61_Students.xlsx
+++ b/backend/sample_files/IT_A_Internal_Marks_61_Students.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,7 +424,7 @@
         <v>922524205125</v>
       </c>
       <c r="B2" t="str">
-        <v>PRIYANKA M.K</v>
+        <v>Priyanka M.K</v>
       </c>
       <c r="C2">
         <v>75</v>
@@ -444,7 +444,7 @@
         <v>922524205126</v>
       </c>
       <c r="B3" t="str">
-        <v>RAGUL R</v>
+        <v>Ragul R</v>
       </c>
       <c r="C3">
         <v>76</v>
@@ -464,7 +464,7 @@
         <v>922524205127</v>
       </c>
       <c r="B4" t="str">
-        <v>RAJASARANYA S</v>
+        <v>Rajasaranya S</v>
       </c>
       <c r="C4">
         <v>77</v>
@@ -484,7 +484,7 @@
         <v>922524205128</v>
       </c>
       <c r="B5" t="str">
-        <v>RAJAVARMAN R A</v>
+        <v>Rajavarman R A</v>
       </c>
       <c r="C5">
         <v>78</v>
@@ -504,7 +504,7 @@
         <v>922524205129</v>
       </c>
       <c r="B6" t="str">
-        <v>RAMAKRISHNAN M</v>
+        <v>Ramakrishnan M</v>
       </c>
       <c r="C6">
         <v>79</v>
@@ -524,7 +524,7 @@
         <v>922524205130</v>
       </c>
       <c r="B7" t="str">
-        <v>RAMKISHORE SM</v>
+        <v>Ramkishore S.M</v>
       </c>
       <c r="C7">
         <v>80</v>
@@ -544,7 +544,7 @@
         <v>922524205131</v>
       </c>
       <c r="B8" t="str">
-        <v>RANJANIDEVI R</v>
+        <v>Ranjanidevi R</v>
       </c>
       <c r="C8">
         <v>81</v>
@@ -564,7 +564,7 @@
         <v>922524205132</v>
       </c>
       <c r="B9" t="str">
-        <v>RANJITH KUMAR S</v>
+        <v>Ranjith Kumar S</v>
       </c>
       <c r="C9">
         <v>82</v>
@@ -584,7 +584,7 @@
         <v>922524205133</v>
       </c>
       <c r="B10" t="str">
-        <v>RANKANAYAKI V</v>
+        <v>Rankanayaki V</v>
       </c>
       <c r="C10">
         <v>83</v>
@@ -604,7 +604,7 @@
         <v>922524205134</v>
       </c>
       <c r="B11" t="str">
-        <v>RIFA NOWREEN NATHAR EM</v>
+        <v>Rifa Nowreen Nathar E.M</v>
       </c>
       <c r="C11">
         <v>84</v>
@@ -624,7 +624,7 @@
         <v>922524205135</v>
       </c>
       <c r="B12" t="str">
-        <v>RITHEESHVER G</v>
+        <v>Ritheeshver G</v>
       </c>
       <c r="C12">
         <v>85</v>
@@ -644,7 +644,7 @@
         <v>922524205136</v>
       </c>
       <c r="B13" t="str">
-        <v>ROHITHSHARMA M</v>
+        <v>Rohithsharma M</v>
       </c>
       <c r="C13">
         <v>86</v>
@@ -664,7 +664,7 @@
         <v>922524205137</v>
       </c>
       <c r="B14" t="str">
-        <v>ROSHAN SAFIHA B</v>
+        <v>Roshan Safiha B</v>
       </c>
       <c r="C14">
         <v>87</v>
@@ -684,7 +684,7 @@
         <v>922524205138</v>
       </c>
       <c r="B15" t="str">
-        <v>SABARI VASAN S</v>
+        <v>Sabari Vasan S</v>
       </c>
       <c r="C15">
         <v>88</v>
@@ -704,7 +704,7 @@
         <v>922524205139</v>
       </c>
       <c r="B16" t="str">
-        <v>SABITHA P</v>
+        <v>Sabitha P</v>
       </c>
       <c r="C16">
         <v>89</v>
@@ -724,7 +724,7 @@
         <v>922524205140</v>
       </c>
       <c r="B17" t="str">
-        <v>SAKTHIVEL S</v>
+        <v>Sakthivel S</v>
       </c>
       <c r="C17">
         <v>90</v>
@@ -744,7 +744,7 @@
         <v>922524205141</v>
       </c>
       <c r="B18" t="str">
-        <v>SALETH JOSELA A</v>
+        <v>Saleth Josela A</v>
       </c>
       <c r="C18">
         <v>91</v>
@@ -764,7 +764,7 @@
         <v>922524205142</v>
       </c>
       <c r="B19" t="str">
-        <v>SANJAY K</v>
+        <v>Sanjay K</v>
       </c>
       <c r="C19">
         <v>92</v>
@@ -784,7 +784,7 @@
         <v>922524205143</v>
       </c>
       <c r="B20" t="str">
-        <v>SANJAY S</v>
+        <v>Sanjay S</v>
       </c>
       <c r="C20">
         <v>93</v>
@@ -804,7 +804,7 @@
         <v>922524205144</v>
       </c>
       <c r="B21" t="str">
-        <v>SANJEEVANI M M</v>
+        <v>Sanjeevani M M</v>
       </c>
       <c r="C21">
         <v>94</v>
@@ -824,7 +824,7 @@
         <v>922524205145</v>
       </c>
       <c r="B22" t="str">
-        <v>SANTHIYA B K</v>
+        <v>Santhiya B K</v>
       </c>
       <c r="C22">
         <v>95</v>
@@ -844,7 +844,7 @@
         <v>922524205146</v>
       </c>
       <c r="B23" t="str">
-        <v>SANTHOSH KUMAR R</v>
+        <v>Santhoshkumar R</v>
       </c>
       <c r="C23">
         <v>96</v>
@@ -864,7 +864,7 @@
         <v>922524205147</v>
       </c>
       <c r="B24" t="str">
-        <v>SANTHOSH S</v>
+        <v>Santhosh S</v>
       </c>
       <c r="C24">
         <v>97</v>
@@ -884,7 +884,7 @@
         <v>922524205148</v>
       </c>
       <c r="B25" t="str">
-        <v>SANTHOSHKUMAR S</v>
+        <v>Santhoshkumar S</v>
       </c>
       <c r="C25">
         <v>98</v>
@@ -904,7 +904,7 @@
         <v>922524205149</v>
       </c>
       <c r="B26" t="str">
-        <v>SARAVANAN P</v>
+        <v>Saravanan P</v>
       </c>
       <c r="C26">
         <v>99</v>
@@ -924,7 +924,7 @@
         <v>922524205150</v>
       </c>
       <c r="B27" t="str">
-        <v>SARMILA V</v>
+        <v>Sarmila V</v>
       </c>
       <c r="C27">
         <v>75</v>
@@ -944,7 +944,7 @@
         <v>922524205151</v>
       </c>
       <c r="B28" t="str">
-        <v>SATHISH KUMAR P</v>
+        <v>Sathish Kumar P</v>
       </c>
       <c r="C28">
         <v>76</v>
@@ -964,7 +964,7 @@
         <v>922524205152</v>
       </c>
       <c r="B29" t="str">
-        <v>SELVARAJ D</v>
+        <v>Selvaraj D</v>
       </c>
       <c r="C29">
         <v>77</v>
@@ -984,7 +984,7 @@
         <v>922524205153</v>
       </c>
       <c r="B30" t="str">
-        <v>SHARUPRAKASH P</v>
+        <v>Sharuprakash P</v>
       </c>
       <c r="C30">
         <v>78</v>
@@ -1004,7 +1004,7 @@
         <v>922524205154</v>
       </c>
       <c r="B31" t="str">
-        <v>SHRINITHI V</v>
+        <v>Shrinithi V</v>
       </c>
       <c r="C31">
         <v>79</v>
@@ -1024,7 +1024,7 @@
         <v>922524205155</v>
       </c>
       <c r="B32" t="str">
-        <v>SIVAPRASANTH S</v>
+        <v>Sivaprasanth S</v>
       </c>
       <c r="C32">
         <v>80</v>
@@ -1044,7 +1044,7 @@
         <v>922524205156</v>
       </c>
       <c r="B33" t="str">
-        <v>SRIJANANI P</v>
+        <v>Srijanani P</v>
       </c>
       <c r="C33">
         <v>81</v>
@@ -1064,7 +1064,7 @@
         <v>922524205157</v>
       </c>
       <c r="B34" t="str">
-        <v>SRINIDI R</v>
+        <v>Srinidi R</v>
       </c>
       <c r="C34">
         <v>82</v>
@@ -1084,7 +1084,7 @@
         <v>922524205159</v>
       </c>
       <c r="B35" t="str">
-        <v>SUJI M</v>
+        <v>Suji M</v>
       </c>
       <c r="C35">
         <v>83</v>
@@ -1104,7 +1104,7 @@
         <v>922524205160</v>
       </c>
       <c r="B36" t="str">
-        <v>SUJITH R</v>
+        <v>Sujith R</v>
       </c>
       <c r="C36">
         <v>84</v>
@@ -1124,7 +1124,7 @@
         <v>922524205161</v>
       </c>
       <c r="B37" t="str">
-        <v>SUPREYA M K</v>
+        <v>Supreya M K</v>
       </c>
       <c r="C37">
         <v>85</v>
@@ -1144,7 +1144,7 @@
         <v>922524205162</v>
       </c>
       <c r="B38" t="str">
-        <v>SURIYAPRIYA V</v>
+        <v>Suriyapriya V</v>
       </c>
       <c r="C38">
         <v>86</v>
@@ -1164,7 +1164,7 @@
         <v>922524205163</v>
       </c>
       <c r="B39" t="str">
-        <v>SUVATHI N</v>
+        <v>Suvathi N</v>
       </c>
       <c r="C39">
         <v>87</v>
@@ -1184,7 +1184,7 @@
         <v>922524205164</v>
       </c>
       <c r="B40" t="str">
-        <v>SWATHI C</v>
+        <v>Swathi C</v>
       </c>
       <c r="C40">
         <v>88</v>
@@ -1204,7 +1204,7 @@
         <v>922524205165</v>
       </c>
       <c r="B41" t="str">
-        <v>SWATHI R</v>
+        <v>Swathi R</v>
       </c>
       <c r="C41">
         <v>89</v>
@@ -1224,7 +1224,7 @@
         <v>922524205166</v>
       </c>
       <c r="B42" t="str">
-        <v>SWETHAA V</v>
+        <v>Swethaa V</v>
       </c>
       <c r="C42">
         <v>90</v>
@@ -1244,7 +1244,7 @@
         <v>922524205167</v>
       </c>
       <c r="B43" t="str">
-        <v>TARUN KARTHICK G</v>
+        <v>Tarun Karthick G</v>
       </c>
       <c r="C43">
         <v>91</v>
@@ -1264,7 +1264,7 @@
         <v>922524205168</v>
       </c>
       <c r="B44" t="str">
-        <v>THAMILNESAN I</v>
+        <v>Thamilnesan I</v>
       </c>
       <c r="C44">
         <v>92</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>922524205169</v>
+        <v>922524205170</v>
       </c>
       <c r="B45" t="str">
-        <v>THARANEESH D</v>
+        <v>Tharani T</v>
       </c>
       <c r="C45">
         <v>93</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>922524205170</v>
+        <v>922524205171</v>
       </c>
       <c r="B46" t="str">
-        <v>THARANI T</v>
+        <v>Tharunkumar K</v>
       </c>
       <c r="C46">
         <v>94</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>922524205171</v>
+        <v>922524205172</v>
       </c>
       <c r="B47" t="str">
-        <v>THARUNKUMAR K</v>
+        <v>Theerthagiri J</v>
       </c>
       <c r="C47">
         <v>95</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>922524205172</v>
+        <v>922524205173</v>
       </c>
       <c r="B48" t="str">
-        <v>THEERTHAGIRI J</v>
+        <v>Thiruvasagam V</v>
       </c>
       <c r="C48">
         <v>96</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>922524205173</v>
+        <v>922524205174</v>
       </c>
       <c r="B49" t="str">
-        <v>THIRUVASAGAM V</v>
+        <v>Vanitha M</v>
       </c>
       <c r="C49">
         <v>97</v>
@@ -1381,10 +1381,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>922524205174</v>
+        <v>922524205175</v>
       </c>
       <c r="B50" t="str">
-        <v>VANITHA M</v>
+        <v>Varsha S</v>
       </c>
       <c r="C50">
         <v>98</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>922524205175</v>
+        <v>922524205176</v>
       </c>
       <c r="B51" t="str">
-        <v>VARSHA S</v>
+        <v>Varsheni T</v>
       </c>
       <c r="C51">
         <v>99</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>922524205176</v>
+        <v>922524205177</v>
       </c>
       <c r="B52" t="str">
-        <v>VARSHENI T</v>
+        <v>Varshini S S</v>
       </c>
       <c r="C52">
         <v>75</v>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>922524205177</v>
+        <v>922524205178</v>
       </c>
       <c r="B53" t="str">
-        <v>VARSHINI S S</v>
+        <v>Vikash S</v>
       </c>
       <c r="C53">
         <v>76</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>922524205178</v>
+        <v>922524205179</v>
       </c>
       <c r="B54" t="str">
-        <v>VIKASH S</v>
+        <v>Vishalini B</v>
       </c>
       <c r="C54">
         <v>77</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>922524205179</v>
+        <v>922524205180</v>
       </c>
       <c r="B55" t="str">
-        <v>VISHALINI B</v>
+        <v>Yamuna E</v>
       </c>
       <c r="C55">
         <v>78</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>922524205180</v>
+        <v>922524205181</v>
       </c>
       <c r="B56" t="str">
-        <v>YAMUNA E</v>
+        <v>Yogadharshini S</v>
       </c>
       <c r="C56">
         <v>79</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>922524205181</v>
+        <v>922524205182</v>
       </c>
       <c r="B57" t="str">
-        <v>YOGADHARSHINI S</v>
+        <v>Yogesh R</v>
       </c>
       <c r="C57">
         <v>80</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>922524205182</v>
+        <v>922524205183</v>
       </c>
       <c r="B58" t="str">
-        <v>YOGESH R</v>
+        <v>Yuvanesh P</v>
       </c>
       <c r="C58">
         <v>81</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>922524205183</v>
+        <v>922524205184</v>
       </c>
       <c r="B59" t="str">
-        <v>YUVANESH P</v>
+        <v>Yuvansankar K</v>
       </c>
       <c r="C59">
         <v>82</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>922524205184</v>
+        <v>922524205185</v>
       </c>
       <c r="B60" t="str">
-        <v>YUVANSANKAR K</v>
+        <v>Srilekha S.C</v>
       </c>
       <c r="C60">
         <v>83</v>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>922524205185</v>
+        <v>922524205303</v>
       </c>
       <c r="B61" t="str">
-        <v>SRILEKHA SC</v>
+        <v>Nadar Prakash Shivahakthivel S</v>
       </c>
       <c r="C61">
         <v>84</v>
@@ -1619,29 +1619,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>922524205303</v>
-      </c>
-      <c r="B62" t="str">
-        <v>NADAR PRAKASH SHIVAHAKTHIVEL S</v>
-      </c>
-      <c r="C62">
-        <v>85</v>
-      </c>
-      <c r="D62">
-        <v>70</v>
-      </c>
-      <c r="E62">
-        <v>72</v>
-      </c>
-      <c r="F62">
-        <v>80</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F61"/>
   </ignoredErrors>
 </worksheet>
 </file>